--- a/Anomaly_Synthesis_Papers_Benchmark_2021_2026.xlsx
+++ b/Anomaly_Synthesis_Papers_Benchmark_2021_2026.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T39"/>
+  <dimension ref="A1:T42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4500,6 +4500,204 @@
           <t>N/A</t>
         </is>
       </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Distribution-hypothesis / Feature-space Anomaly Synthesis</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Do You Need Text Rectification? Soft Attention Mask Embedding for Rectification-Free Scene</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Antonio Colombo, Giovanni Bianchi</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>MVTec AD image-level</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="n"/>
+      <c r="K40" s="6" t="n"/>
+      <c r="L40" s="6" t="n"/>
+      <c r="M40" s="6" t="n"/>
+      <c r="N40" s="6" t="n"/>
+      <c r="O40" s="6" t="n"/>
+      <c r="P40" s="6" t="n"/>
+      <c r="Q40" s="6" t="n"/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>Auto-fetched from arXiv; pending verification</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.18173</t>
+        </is>
+      </c>
+      <c r="T40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Distribution-hypothesis / Feature-space Anomaly Synthesis</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Deep learning-based compression of giga-resolution whole slide images</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Maren Høibø, Etienne Gaucher, Ingerid Reinertsen, Marit Valla, Erik Smistad</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>MVTec AD image-level</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="6" t="n"/>
+      <c r="L41" s="6" t="n"/>
+      <c r="M41" s="6" t="n"/>
+      <c r="N41" s="6" t="n"/>
+      <c r="O41" s="6" t="n"/>
+      <c r="P41" s="6" t="n"/>
+      <c r="Q41" s="6" t="n"/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>Auto-fetched from arXiv; pending verification</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.17668</t>
+        </is>
+      </c>
+      <c r="T41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Distribution-hypothesis / Feature-space Anomaly Synthesis</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>EgoKit: Towards Unified Low-Cost Egocentric Data Collection with Heterogeneous Devices</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Liuchuan Yu, Erdem Murat, Beichen Wang, Yan Zeng, Tingting Luo, Huizhen Zhou, Shanghao Li, Huining Feng</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>MVTec AD image-level</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="n"/>
+      <c r="K42" s="6" t="n"/>
+      <c r="L42" s="6" t="n"/>
+      <c r="M42" s="6" t="n"/>
+      <c r="N42" s="6" t="n"/>
+      <c r="O42" s="6" t="n"/>
+      <c r="P42" s="6" t="n"/>
+      <c r="Q42" s="6" t="n"/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>Auto-fetched from arXiv; pending verification</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.16797</t>
+        </is>
+      </c>
+      <c r="T42" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
@@ -13753,7 +13951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -14380,6 +14578,204 @@
         <f>HYPERLINK("https://github.com/VitjanZ/DRAEM","GitHub")</f>
         <v/>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Distribution-hypothesis / Feature-space Anomaly Synthesis</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Do You Need Text Rectification? Soft Attention Mask Embedding for Rectification-Free Scene</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Antonio Colombo, Giovanni Bianchi</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>MVTec AD image-level</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="n"/>
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="10" t="n"/>
+      <c r="R7" s="10" t="inlineStr">
+        <is>
+          <t>Auto-fetched from arXiv; pending verification</t>
+        </is>
+      </c>
+      <c r="S7" s="11" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.18173</t>
+        </is>
+      </c>
+      <c r="T7" s="11" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Distribution-hypothesis / Feature-space Anomaly Synthesis</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Deep learning-based compression of giga-resolution whole slide images</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Maren Høibø, Etienne Gaucher, Ingerid Reinertsen, Marit Valla, Erik Smistad</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>MVTec AD image-level</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="n"/>
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="10" t="n"/>
+      <c r="O8" s="10" t="n"/>
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="10" t="n"/>
+      <c r="R8" s="10" t="inlineStr">
+        <is>
+          <t>Auto-fetched from arXiv; pending verification</t>
+        </is>
+      </c>
+      <c r="S8" s="11" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.17668</t>
+        </is>
+      </c>
+      <c r="T8" s="11" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Distribution-hypothesis / Feature-space Anomaly Synthesis</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>EgoKit: Towards Unified Low-Cost Egocentric Data Collection with Heterogeneous Devices</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Liuchuan Yu, Erdem Murat, Beichen Wang, Yan Zeng, Tingting Luo, Huizhen Zhou, Shanghao Li, Huining Feng</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>MVTec AD image-level</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="n"/>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="10" t="n"/>
+      <c r="R9" s="10" t="inlineStr">
+        <is>
+          <t>Auto-fetched from arXiv; pending verification</t>
+        </is>
+      </c>
+      <c r="S9" s="11" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.16797</t>
+        </is>
+      </c>
+      <c r="T9" s="11" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>

--- a/Anomaly_Synthesis_Papers_Benchmark_2021_2026.xlsx
+++ b/Anomaly_Synthesis_Papers_Benchmark_2021_2026.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T42"/>
+  <dimension ref="A1:T45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4698,6 +4698,204 @@
         </is>
       </c>
       <c r="T42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Vision-language / Foundation-model-based Anomaly Synthesis</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Mags-RL: Wearing Multimodal LLMs a Magnifying Glass via Agentic Reinforcement Learning For</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Xuanzhao Dong, Wenhui Zhu, Peijie Qiu, Xiwen Chen, Xiaobing Yu, Xin Li, Zhipeng Wang, Shao Tang</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>MVTec AD image-level</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="n"/>
+      <c r="K43" s="6" t="n"/>
+      <c r="L43" s="6" t="n"/>
+      <c r="M43" s="6" t="n"/>
+      <c r="N43" s="6" t="n"/>
+      <c r="O43" s="6" t="n"/>
+      <c r="P43" s="6" t="n"/>
+      <c r="Q43" s="6" t="n"/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>Auto-fetched from arXiv; pending verification</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.27960</t>
+        </is>
+      </c>
+      <c r="T43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Distribution-hypothesis / Feature-space Anomaly Synthesis</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Mahalanobis PatchCore: Covariance-Aware and Streaming-Compatible Industrial Anomaly Detect</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Niccolò Ferrari, Oligert Osmani, Evelina Lamma</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>MVTec AD image-level</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="n"/>
+      <c r="K44" s="6" t="n"/>
+      <c r="L44" s="6" t="n"/>
+      <c r="M44" s="6" t="n"/>
+      <c r="N44" s="6" t="n"/>
+      <c r="O44" s="6" t="n"/>
+      <c r="P44" s="6" t="n"/>
+      <c r="Q44" s="6" t="n"/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>Auto-fetched from arXiv; pending verification</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.27748</t>
+        </is>
+      </c>
+      <c r="T44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Distribution-hypothesis / Feature-space Anomaly Synthesis</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Beyond Motion Primitives: Behavioral Activity Recognition from Head-Mounted IMU</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Chung-Ta Huang, Leopold Das, Jeffrey Zhou, Faizaan Siddique, Julia Seungjoo Baek, Serena Liu, Andrew Rusli, Todd Y. Zhou</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>MVTec AD image-level</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="n"/>
+      <c r="K45" s="6" t="n"/>
+      <c r="L45" s="6" t="n"/>
+      <c r="M45" s="6" t="n"/>
+      <c r="N45" s="6" t="n"/>
+      <c r="O45" s="6" t="n"/>
+      <c r="P45" s="6" t="n"/>
+      <c r="Q45" s="6" t="n"/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>Auto-fetched from arXiv; pending verification</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.27464</t>
+        </is>
+      </c>
+      <c r="T45" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
@@ -13951,7 +14149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -14776,6 +14974,204 @@
         </is>
       </c>
       <c r="T9" s="11" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Vision-language / Foundation-model-based Anomaly Synthesis</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Mags-RL: Wearing Multimodal LLMs a Magnifying Glass via Agentic Reinforcement Learning For</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Xuanzhao Dong, Wenhui Zhu, Peijie Qiu, Xiwen Chen, Xiaobing Yu, Xin Li, Zhipeng Wang, Shao Tang</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>MVTec AD image-level</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n"/>
+      <c r="O10" s="10" t="n"/>
+      <c r="P10" s="10" t="n"/>
+      <c r="Q10" s="10" t="n"/>
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>Auto-fetched from arXiv; pending verification</t>
+        </is>
+      </c>
+      <c r="S10" s="11" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.27960</t>
+        </is>
+      </c>
+      <c r="T10" s="11" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Distribution-hypothesis / Feature-space Anomaly Synthesis</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Mahalanobis PatchCore: Covariance-Aware and Streaming-Compatible Industrial Anomaly Detect</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Niccolò Ferrari, Oligert Osmani, Evelina Lamma</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>MVTec AD image-level</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="n"/>
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="10" t="n"/>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="10" t="n"/>
+      <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="10" t="n"/>
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>Auto-fetched from arXiv; pending verification</t>
+        </is>
+      </c>
+      <c r="S11" s="11" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.27748</t>
+        </is>
+      </c>
+      <c r="T11" s="11" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Distribution-hypothesis / Feature-space Anomaly Synthesis</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Beyond Motion Primitives: Behavioral Activity Recognition from Head-Mounted IMU</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Chung-Ta Huang, Leopold Das, Jeffrey Zhou, Faizaan Siddique, Julia Seungjoo Baek, Serena Liu, Andrew Rusli, Todd Y. Zhou</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>MVTec AD image-level</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="n"/>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n"/>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="n"/>
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="10" t="n"/>
+      <c r="R12" s="10" t="inlineStr">
+        <is>
+          <t>Auto-fetched from arXiv; pending verification</t>
+        </is>
+      </c>
+      <c r="S12" s="11" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.27464</t>
+        </is>
+      </c>
+      <c r="T12" s="11" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
